--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.30976728831747</v>
+        <v>7.850337184351589</v>
       </c>
       <c r="D2" t="n">
-        <v>48.73705614889708</v>
+        <v>7.919771624195775</v>
       </c>
       <c r="E2" t="n">
-        <v>18.53956509684489</v>
+        <v>3.012679328237295</v>
       </c>
       <c r="F2" t="n">
-        <v>8.752697660454878</v>
+        <v>1.422313369823918</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.55311912397611</v>
+        <v>3.989881857646117</v>
       </c>
       <c r="D3" t="n">
-        <v>25.33687615914177</v>
+        <v>4.117242375860537</v>
       </c>
       <c r="E3" t="n">
-        <v>18.53956509684489</v>
+        <v>3.012679328237295</v>
       </c>
       <c r="F3" t="n">
-        <v>8.752697660454878</v>
+        <v>1.422313369823918</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.79258358449126</v>
+        <v>3.37879483247983</v>
       </c>
       <c r="D4" t="n">
-        <v>21.21430461957493</v>
+        <v>3.447324500680926</v>
       </c>
       <c r="E4" t="n">
-        <v>18.53956509684489</v>
+        <v>3.012679328237295</v>
       </c>
       <c r="F4" t="n">
-        <v>8.752697660454878</v>
+        <v>1.422313369823918</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.33586763966689</v>
+        <v>4.92957849144587</v>
       </c>
       <c r="D5" t="n">
-        <v>29.89615449895608</v>
+        <v>4.858125106080363</v>
       </c>
       <c r="E5" t="n">
-        <v>18.53956509684489</v>
+        <v>3.012679328237295</v>
       </c>
       <c r="F5" t="n">
-        <v>8.752697660454878</v>
+        <v>1.422313369823918</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.81370298859376</v>
+        <v>4.357226735646487</v>
       </c>
       <c r="D6" t="n">
-        <v>27.05518352052586</v>
+        <v>4.396467322085453</v>
       </c>
       <c r="E6" t="n">
-        <v>18.53956509684489</v>
+        <v>3.012679328237295</v>
       </c>
       <c r="F6" t="n">
-        <v>8.752697660454878</v>
+        <v>1.422313369823918</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>74.01254711420815</v>
+        <v>12.02703890605882</v>
       </c>
       <c r="D7" t="n">
-        <v>28.91106022134316</v>
+        <v>4.698047285968263</v>
       </c>
       <c r="E7" t="n">
-        <v>18.53956509684489</v>
+        <v>3.012679328237295</v>
       </c>
       <c r="F7" t="n">
-        <v>8.752697660454878</v>
+        <v>1.422313369823918</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
